--- a/Assets/ExcelImporter/EnemyGroup/EnemyGroup_SO.xlsx
+++ b/Assets/ExcelImporter/EnemyGroup/EnemyGroup_SO.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14040"/>
+    <workbookView windowWidth="29400" windowHeight="12380"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>uid</t>
   </si>
@@ -60,6 +60,12 @@
   </si>
   <si>
     <t>[0,16,28,28,28]</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>[0,2,14,16,28]</t>
   </si>
 </sst>
 </file>
@@ -1229,8 +1235,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17" customHeight="1" outlineLevelRow="3" outlineLevelCol="4"/>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="17" customHeight="1" outlineLevelRow="4" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12.0096153846154" style="1" customWidth="1"/>
     <col min="2" max="2" width="14.0961538461538" style="1" customWidth="1"/>
@@ -1271,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="E2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:5">
@@ -1288,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="E3" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:5">
@@ -1305,6 +1311,23 @@
         <v>10</v>
       </c>
       <c r="E4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1">
         <v>1</v>
       </c>
     </row>
